--- a/ESM_21.xlsx
+++ b/ESM_21.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30527"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F19E1105-5EF0-42DC-981A-8C3C5B7B7DB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8B83333-A496-40CD-95F1-9556B853E965}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="47">
   <si>
     <t>mesh</t>
   </si>
@@ -139,13 +139,31 @@
   </si>
   <si>
     <t>Used for calibration and validation of the single-track thermal-CFD model and for comparison with the AM-Bench 2022 experimental data.</t>
+  </si>
+  <si>
+    <t>Δx ( micron)</t>
+  </si>
+  <si>
+    <t>Δy (­micron)</t>
+  </si>
+  <si>
+    <t>Δz (­micron)</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>5</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -170,6 +188,11 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -207,7 +230,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -227,14 +250,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="11" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="11" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -583,10 +610,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="9"/>
+      <c r="B1" s="12"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
@@ -695,245 +722,320 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="5" width="13.5546875" customWidth="1"/>
-    <col min="6" max="6" width="20.5546875" customWidth="1"/>
-    <col min="7" max="8" width="13.5546875" customWidth="1"/>
-    <col min="9" max="12" width="13.5546875" style="12" customWidth="1"/>
-    <col min="13" max="24" width="13.5546875" customWidth="1"/>
+    <col min="1" max="8" width="13.5546875" customWidth="1"/>
+    <col min="9" max="9" width="20.5546875" customWidth="1"/>
+    <col min="10" max="11" width="13.5546875" customWidth="1"/>
+    <col min="12" max="15" width="13.5546875" style="11" customWidth="1"/>
+    <col min="16" max="27" width="13.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="L1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="M1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="N1" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="10" t="s">
+      <c r="O1" s="9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="E2" s="2">
         <v>559680</v>
       </c>
-      <c r="C2" s="3">
+      <c r="F2" s="3">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="D2">
+      <c r="G2">
         <v>2</v>
       </c>
-      <c r="E2">
+      <c r="H2">
         <v>140.16999999999999</v>
       </c>
-      <c r="F2">
+      <c r="I2">
         <v>135.55000000000001</v>
       </c>
-      <c r="G2">
+      <c r="J2">
         <v>13200</v>
       </c>
-      <c r="H2">
+      <c r="K2">
         <v>3692</v>
       </c>
-      <c r="I2" s="11">
+      <c r="L2" s="10">
         <v>-887080</v>
       </c>
-      <c r="J2" s="11">
+      <c r="M2" s="10">
         <v>-260208</v>
       </c>
-      <c r="K2" s="11">
+      <c r="N2" s="10">
         <v>-443932</v>
       </c>
-      <c r="L2" s="11">
+      <c r="O2" s="10">
         <v>1.1640000000000003E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="E3" s="2">
         <v>295680</v>
       </c>
-      <c r="C3" s="3">
+      <c r="F3" s="3">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="D3">
+      <c r="G3">
         <v>2</v>
       </c>
-      <c r="E3">
+      <c r="H3">
         <v>141.12</v>
       </c>
-      <c r="F3">
+      <c r="I3">
         <v>135.28</v>
       </c>
-      <c r="G3">
+      <c r="J3">
         <v>13211</v>
       </c>
-      <c r="H3">
+      <c r="K3">
         <v>3680</v>
       </c>
-      <c r="I3" s="11">
+      <c r="L3" s="10">
         <v>-879092</v>
       </c>
-      <c r="J3" s="11">
+      <c r="M3" s="10">
         <v>-263664</v>
       </c>
-      <c r="K3" s="11">
+      <c r="N3" s="10">
         <v>-446212</v>
       </c>
-      <c r="L3" s="11">
+      <c r="O3" s="10">
         <v>1.1580000000000004E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="E4" s="2">
         <v>147840</v>
       </c>
-      <c r="C4" s="3">
+      <c r="F4" s="3">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="D4">
+      <c r="G4">
         <v>2</v>
       </c>
-      <c r="E4">
+      <c r="H4">
         <v>141.21</v>
       </c>
-      <c r="F4">
+      <c r="I4">
         <v>135.25</v>
       </c>
-      <c r="G4">
+      <c r="J4">
         <v>13218</v>
       </c>
-      <c r="H4">
+      <c r="K4">
         <v>3682</v>
       </c>
-      <c r="I4" s="11">
+      <c r="L4" s="10">
         <v>-875348</v>
       </c>
-      <c r="J4" s="11">
+      <c r="M4" s="10">
         <v>-265152</v>
       </c>
-      <c r="K4" s="11">
+      <c r="N4" s="10">
         <v>-440976</v>
       </c>
-      <c r="L4" s="11">
+      <c r="O4" s="10">
         <v>1.1580000000000004E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="E5" s="2">
         <v>43200</v>
       </c>
-      <c r="C5" s="3">
+      <c r="F5" s="3">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="D5">
+      <c r="G5">
         <v>2</v>
       </c>
-      <c r="E5">
+      <c r="H5">
         <v>148.11000000000001</v>
       </c>
-      <c r="F5">
+      <c r="I5">
         <v>140.25</v>
       </c>
-      <c r="G5">
+      <c r="J5">
         <v>14224</v>
       </c>
-      <c r="H5">
+      <c r="K5">
         <v>3590</v>
       </c>
-      <c r="I5" s="11">
+      <c r="L5" s="10">
         <v>-763944</v>
       </c>
-      <c r="J5" s="11">
+      <c r="M5" s="10">
         <v>-262620</v>
       </c>
-      <c r="K5" s="11">
+      <c r="N5" s="10">
         <v>-464904</v>
       </c>
-      <c r="L5" s="11">
+      <c r="O5" s="10">
         <v>1.1379999999999997E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
